--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +210 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +382 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.039</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 3,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +382 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +210 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.039</v>
+        <v>0.049</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 26/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 27/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 27/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 28/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 28/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 29/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 29/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 30/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 30/09/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 01/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 02/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 03/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 04/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 05/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 06/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 07/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 08/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 09/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 10/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 11/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 12/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -929,7 +929,7 @@
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 4,9 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +210 €/mois.</t>
+          <t>EN CLAIR — Sur la base d'un loyer ESTIMÉ (pas de bail signé à ce stade) : aux hypothèses de ce dossier (apport 20 %, crédit 5,34 % sur 20 ans, charges provisionnées), le bien s'autofinance : le loyer couvre crédit et charges et laisse environ +132 €/mois.</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1082,7 @@
         </is>
       </c>
       <c r="B28" s="20" t="n">
-        <v>0.049</v>
+        <v>0.0534</v>
       </c>
     </row>
     <row r="29">

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 13/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 14/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 15/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 16/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 17/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 18/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 19/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 20/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 21/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 22/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 23/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 24/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>

--- a/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
+++ b/docs/dossiers/dossier-saint-mande-7b831bdf.xlsx
@@ -833,7 +833,7 @@
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
         <is>
-          <t>Dossier généré le 25/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
+          <t>Dossier généré le 26/10/2026 — indicatif, l'offre de prêt de la banque fait foi.</t>
         </is>
       </c>
     </row>
@@ -2297,7 +2297,7 @@
       </c>
       <c r="B11" s="29" t="inlineStr">
         <is>
-          <t>loyer_estime</t>
+          <t>loyer_estime · surface_a_ventiler · occupation_a_confirmer</t>
         </is>
       </c>
     </row>
